--- a/数值表格/怪物相关数值表格.xlsx
+++ b/数值表格/怪物相关数值表格.xlsx
@@ -3948,12 +3948,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
